--- a/personal_forms/006_couples_survey--personal_forms.xlsx
+++ b/personal_forms/006_couples_survey--personal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rather_not_tell</t>
+          <t>rather not tell</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rather_not_tell</t>
+          <t>rather not tell</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>romantic_relationship</t>
+          <t>romantic relationship</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>family_member</t>
+          <t>family member</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>in_a_relationship</t>
+          <t>in a relationship</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>not_married</t>
+          <t>not married</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rather_not_tell</t>
+          <t>rather not tell</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>in_a_relationship</t>
+          <t>in a relationship</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>not_married</t>
+          <t>not married</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>rather_not_tell</t>
+          <t>rather not tell</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>not_satisfied</t>
+          <t>not satisfied</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>not_satisfied</t>
+          <t>not satisfied</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>not_trusted</t>
+          <t>not trusted</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>not_trusted</t>
+          <t>not trusted</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>not_fear</t>
+          <t>not fear</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>not_fear</t>
+          <t>not fear</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>not_safe</t>
+          <t>not safe</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>not_safe</t>
+          <t>not safe</t>
         </is>
       </c>
     </row>
